--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,45 +1007,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105891984</v>
+        <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92333</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673203</v>
+        <v>673358</v>
       </c>
       <c r="R5" t="n">
-        <v>6636322</v>
+        <v>6636459</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,12 +1072,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,75 +1098,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Helene Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105891984</t>
+          <t>https://artportalen.se/Sighting/135958070</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92746724</v>
+        <v>105891984</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673278</v>
+        <v>673203</v>
       </c>
       <c r="R6" t="n">
-        <v>6636430</v>
+        <v>6636322</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,28 +1200,33 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Via Helene Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92746724</t>
+          <t>https://artportalen.se/Sighting/105891984</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121064402</v>
+        <v>92746724</v>
       </c>
       <c r="B7" t="n">
         <v>93197</v>
@@ -1246,19 +1255,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Södermossen, Almunge, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672992</v>
+        <v>673278</v>
       </c>
       <c r="R7" t="n">
-        <v>6636150</v>
+        <v>6636430</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,16 +1323,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121064402</t>
+          <t>https://artportalen.se/Sighting/92746724</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>92747418</v>
+        <v>121064402</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,38 +1340,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Upl</t>
+          <t>Södermossen, Almunge, Södermossen, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673160</v>
+        <v>672992</v>
       </c>
       <c r="R8" t="n">
-        <v>6636234</v>
+        <v>6636150</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,12 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,38 +1425,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92747418</t>
+          <t>https://artportalen.se/Sighting/121064402</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92747682</v>
+        <v>92747418</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673223</v>
+        <v>673160</v>
       </c>
       <c r="R9" t="n">
-        <v>6636197</v>
+        <v>6636234</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1519,16 +1528,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92747682</t>
+          <t>https://artportalen.se/Sighting/92747418</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92747916</v>
+        <v>92747682</v>
       </c>
       <c r="B10" t="n">
-        <v>91282</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673323</v>
+        <v>673223</v>
       </c>
       <c r="R10" t="n">
-        <v>6636146</v>
+        <v>6636197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1622,54 +1631,55 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92747916</t>
+          <t>https://artportalen.se/Sighting/92747682</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105314260</v>
+        <v>92747916</v>
       </c>
       <c r="B11" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskarkärret, Upl</t>
+          <t>Södermossen, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672916</v>
+        <v>673323</v>
       </c>
       <c r="R11" t="n">
-        <v>6636028</v>
+        <v>6636146</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,41 +1719,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sent men tydliga fruktkroppar.</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105314260</t>
+          <t>https://artportalen.se/Sighting/92747916</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92747998</v>
+        <v>105314260</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,38 +1751,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Upl</t>
+          <t>Fiskarkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673318</v>
+        <v>672916</v>
       </c>
       <c r="R12" t="n">
-        <v>6636108</v>
+        <v>6636028</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,12 +1805,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,28 +1821,38 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sent men tydliga fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92747998</t>
+          <t>https://artportalen.se/Sighting/105314260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>92889491</v>
+        <v>92747998</v>
       </c>
       <c r="B13" t="n">
         <v>79946</v>
@@ -1875,14 +1884,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Södermossen, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673206</v>
+        <v>673318</v>
       </c>
       <c r="R13" t="n">
-        <v>6636244</v>
+        <v>6636108</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1909,12 +1918,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,24 +1938,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92889491</t>
+          <t>https://artportalen.se/Sighting/92747998</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064388</v>
+        <v>92889491</v>
       </c>
       <c r="B14" t="n">
         <v>79946</v>
@@ -1975,19 +1984,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Södermossen, Almunge, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672992</v>
+        <v>673206</v>
       </c>
       <c r="R14" t="n">
-        <v>6636150</v>
+        <v>6636244</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,12 +2021,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,27 +2041,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121064388</t>
+          <t>https://artportalen.se/Sighting/92889491</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106175095</v>
+        <v>121064388</v>
       </c>
       <c r="B15" t="n">
-        <v>6284</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2059,46 +2069,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100524</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sågarbol, Upl</t>
+          <t>Södermossen, Almunge, Södermossen, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673370</v>
+        <v>672992</v>
       </c>
       <c r="R15" t="n">
-        <v>6636300</v>
+        <v>6636150</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2122,17 +2123,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>HC12</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,55 +2139,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>timmerticka</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175095</t>
+          <t>https://artportalen.se/Sighting/121064388</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>92745062</v>
+        <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,44 +2171,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Upl</t>
+          <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673464</v>
+        <v>672932</v>
       </c>
       <c r="R16" t="n">
-        <v>6636428</v>
+        <v>6636284</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2260,12 +2230,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,27 +2260,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92745062</t>
+          <t>https://artportalen.se/Sighting/135958064</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106175080</v>
+        <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>25767</v>
+        <v>57977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,31 +2288,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk vedstrit</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cixidia confinis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2341,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673378</v>
+        <v>673267</v>
       </c>
       <c r="R17" t="n">
-        <v>6636015</v>
+        <v>6636455</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2371,17 +2347,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>HC15</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,55 +2373,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>citronticka</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175080</t>
+          <t>https://artportalen.se/Sighting/135958068</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106175079</v>
+        <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>25768</v>
+        <v>57977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,46 +2405,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100659</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673378</v>
+        <v>673374</v>
       </c>
       <c r="R18" t="n">
-        <v>6636015</v>
+        <v>6636428</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2511,17 +2467,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>HC15</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,105 +2493,74 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>citronticka</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175079</t>
+          <t>https://artportalen.se/Sighting/135958071</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100051128</v>
+        <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>57977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672935</v>
+        <v>673429</v>
       </c>
       <c r="R19" t="n">
-        <v>6636217</v>
+        <v>6636497</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,12 +2584,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,27 +2614,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100051128</t>
+          <t>https://artportalen.se/Sighting/135958073</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106175077</v>
+        <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>6274</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,31 +2642,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105336</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2735,13 +2671,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673378</v>
+        <v>672972</v>
       </c>
       <c r="R20" t="n">
-        <v>6636015</v>
+        <v>6636199</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,17 +2701,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>HC15</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,55 +2727,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>citronticka</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Amyloporia xantha # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175077</t>
+          <t>https://artportalen.se/Sighting/135958062</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106175096</v>
+        <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>6274</v>
+        <v>57167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2842,46 +2759,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105336</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673370</v>
+        <v>673386</v>
       </c>
       <c r="R21" t="n">
-        <v>6636300</v>
+        <v>6636551</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2905,17 +2813,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>HC12</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,82 +2839,58 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>timmerticka</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175096</t>
+          <t>https://artportalen.se/Sighting/135958072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106175097</v>
+        <v>106175095</v>
       </c>
       <c r="B22" t="n">
-        <v>6274</v>
+        <v>6284</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105336</v>
+        <v>100524</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3015,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673474</v>
+        <v>673370</v>
       </c>
       <c r="R22" t="n">
-        <v>6636451</v>
+        <v>6636300</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3055,7 +2944,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>HC11</t>
+          <t>HC12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,22 +2958,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>knölticka</t>
+          <t>timmerticka</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Fomitopsis serialis</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fomitopsis serialis # Picea abies</t>
+          <t>Amyloporia sinuosa # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3105,16 +2994,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175097</t>
+          <t>https://artportalen.se/Sighting/106175095</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106175120</v>
+        <v>92745062</v>
       </c>
       <c r="B23" t="n">
-        <v>6274</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3122,46 +3011,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105336</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sågarbol, Upl</t>
+          <t>Södermossen, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672920</v>
+        <v>673464</v>
       </c>
       <c r="R23" t="n">
-        <v>6636119</v>
+        <v>6636428</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3185,17 +3072,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>HC09</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,77 +3088,53 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>timmerticka</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Amyloporia sinuosa # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175120</t>
+          <t>https://artportalen.se/Sighting/92745062</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106175117</v>
+        <v>106175080</v>
       </c>
       <c r="B24" t="n">
-        <v>7673</v>
+        <v>25767</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106431</v>
+        <v>100658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Furuvedvivel</t>
+          <t>Mörk vedstrit</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhyncolus elongatus</t>
+          <t>Cixidia confinis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
+          <t>(Zetterstedt, 1838)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3295,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672920</v>
+        <v>673378</v>
       </c>
       <c r="R24" t="n">
-        <v>6636119</v>
+        <v>6636015</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3335,7 +3193,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>HC09</t>
+          <t>HC15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3349,12 +3207,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>timmerticka</t>
+          <t>citronticka</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Amyloporia xantha</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -3364,7 +3222,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa # Pinus sylvestris</t>
+          <t>Amyloporia xantha # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3385,16 +3243,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106175117</t>
+          <t>https://artportalen.se/Sighting/106175080</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92889153</v>
+        <v>106175079</v>
       </c>
       <c r="B25" t="n">
-        <v>106244</v>
+        <v>25768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,39 +3260,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100659</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södermossen, Almunge, Upl</t>
+          <t>Sågarbol, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672926</v>
+        <v>673378</v>
       </c>
       <c r="R25" t="n">
-        <v>6636229</v>
+        <v>6636015</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3458,12 +3323,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2022-03-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>HC15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3474,67 +3344,91 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>citronticka</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Amyloporia xantha</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Amyloporia xantha # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92889153</t>
+          <t>https://artportalen.se/Sighting/106175079</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100051131</v>
+        <v>100051128</v>
       </c>
       <c r="B26" t="n">
-        <v>106244</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3542,10 +3436,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673458</v>
+        <v>672935</v>
       </c>
       <c r="R26" t="n">
-        <v>6636417</v>
+        <v>6636217</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3586,7 +3480,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3604,7 +3497,1388 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/100051128</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135958067</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>673294</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6636427</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958067</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>106175077</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>673378</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6636015</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>HC15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>citronticka</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Amyloporia xantha</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Amyloporia xantha # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106175077</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>106175096</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>673370</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6636300</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>HC12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>timmerticka</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106175096</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>106175097</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>673474</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6636451</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>HC11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>knölticka</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fomitopsis serialis</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fomitopsis serialis # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106175097</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>106175120</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>672920</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6636119</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>HC09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>timmerticka</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106175120</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>106175117</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7673</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106431</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Furuvedvivel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Rhyncolus elongatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Gyllenhal, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>672920</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6636119</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>HC09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>timmerticka</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106175117</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>92889153</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Södermossen, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>672926</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6636229</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Bengtson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Bengtson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92889153</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>100051131</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>673458</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6636417</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/100051131</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135958063</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>672938</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6636251</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958063</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135958074</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>673455</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6636477</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958074</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135958075</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sågarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>673457</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6636430</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958075</t>
         </is>
       </c>
     </row>
@@ -3635,6 +4909,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135958064</v>
       </c>
       <c r="B16" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>135958068</v>
       </c>
       <c r="B17" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135958071</v>
       </c>
       <c r="B18" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135958073</v>
       </c>
       <c r="B19" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135958062</v>
       </c>
       <c r="B20" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135958072</v>
       </c>
       <c r="B21" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135958067</v>
       </c>
       <c r="B27" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>135958070</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135958074</v>
       </c>
       <c r="B36" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135958075</v>
       </c>
       <c r="B37" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
